--- a/data_quality_tool/tests/MinimalDataModelError.xlsx
+++ b/data_quality_tool/tests/MinimalDataModelError.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">group_variable</t>
   </si>
   <si>
-    <t xml:space="preserve">integer</t>
+    <t xml:space="preserve">discrete</t>
   </si>
   <si>
     <t xml:space="preserve">0-100</t>
